--- a/Semiconductor/RMBS.xlsx
+++ b/Semiconductor/RMBS.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jameelbrannon/Library/CloudStorage/Dropbox/models/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{795D8E61-B06C-204A-B26D-BC7DB21C30A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90C6BA11-51B8-F04B-964D-E5D818E2B7DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7320" yWindow="1020" windowWidth="42800" windowHeight="23260" xr2:uid="{435C723C-60C2-6B4B-9352-FB87DC9C29B5}"/>
+    <workbookView xWindow="7320" yWindow="1020" windowWidth="42800" windowHeight="23260" activeTab="1" xr2:uid="{435C723C-60C2-6B4B-9352-FB87DC9C29B5}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
     <sheet name="Model" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -652,7 +652,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="m/d;@"/>
+    <numFmt numFmtId="164" formatCode="m/d;@"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
@@ -729,7 +729,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -759,19 +759,16 @@
     <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -1243,7 +1240,7 @@
         <f>SUM(Model!J38:J39)</f>
         <v>944657</v>
       </c>
-      <c r="L6" s="19">
+      <c r="L6" s="18">
         <v>46055</v>
       </c>
       <c r="M6" s="1" t="s">
@@ -1257,7 +1254,7 @@
       <c r="I7" s="1">
         <v>0</v>
       </c>
-      <c r="L7" s="19">
+      <c r="L7" s="18">
         <v>45936</v>
       </c>
       <c r="M7" s="1" t="s">
@@ -1272,7 +1269,7 @@
         <f>+I5-I6+I7</f>
         <v>10794313</v>
       </c>
-      <c r="L8" s="19">
+      <c r="L8" s="18">
         <v>45866</v>
       </c>
       <c r="M8" s="1" t="s">
@@ -1283,79 +1280,79 @@
       <c r="B9" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="L9" s="19"/>
+      <c r="L9" s="18"/>
     </row>
     <row r="10" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B10" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="L10" s="19"/>
+      <c r="L10" s="18"/>
     </row>
     <row r="11" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="L11" s="19"/>
+      <c r="L11" s="18"/>
     </row>
     <row r="12" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B12" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="L12" s="19"/>
+      <c r="L12" s="18"/>
     </row>
     <row r="13" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B13" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="L13" s="19"/>
+      <c r="L13" s="18"/>
     </row>
     <row r="14" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B14" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="L14" s="19"/>
+      <c r="L14" s="18"/>
     </row>
     <row r="15" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B15" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="L15" s="19"/>
+      <c r="L15" s="18"/>
     </row>
     <row r="16" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="L16" s="19"/>
+      <c r="L16" s="18"/>
     </row>
     <row r="17" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="L17" s="19"/>
+      <c r="L17" s="18"/>
     </row>
     <row r="18" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="L18" s="19"/>
+      <c r="L18" s="18"/>
     </row>
     <row r="19" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="L19" s="19"/>
+      <c r="L19" s="18"/>
     </row>
     <row r="20" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B20" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="L20" s="19"/>
+      <c r="L20" s="18"/>
     </row>
     <row r="21" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B21" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="L21" s="19"/>
+      <c r="L21" s="18"/>
     </row>
     <row r="22" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B22" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="L22" s="19"/>
+      <c r="L22" s="18"/>
     </row>
     <row r="23" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B23" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="L23" s="19"/>
+      <c r="L23" s="18"/>
     </row>
     <row r="24" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B24" s="1" t="s">
@@ -2707,45 +2704,41 @@
         <v>18</v>
       </c>
       <c r="C14" s="10">
-        <f>+SUM(C11:C13)</f>
+        <f t="shared" ref="C14:K14" si="11">+SUM(C11:C13)</f>
         <v>117871</v>
       </c>
       <c r="D14" s="10">
-        <f>+SUM(D11:D13)</f>
+        <f t="shared" si="11"/>
         <v>132138</v>
       </c>
       <c r="E14" s="10">
-        <f>+SUM(E11:E13)</f>
+        <f t="shared" si="11"/>
         <v>145513</v>
       </c>
       <c r="F14" s="10">
-        <f>+SUM(F11:F13)</f>
+        <f t="shared" si="11"/>
         <v>161102</v>
       </c>
       <c r="G14" s="10">
-        <f>+SUM(G11:G13)</f>
+        <f t="shared" si="11"/>
         <v>166664</v>
       </c>
       <c r="H14" s="10">
-        <f>+SUM(H11:H13)</f>
+        <f t="shared" si="11"/>
         <v>172209</v>
       </c>
       <c r="I14" s="10">
-        <f>+SUM(I11:I13)</f>
+        <f t="shared" si="11"/>
         <v>178513</v>
       </c>
       <c r="J14" s="10">
-        <f>+SUM(J11:J13)</f>
+        <f t="shared" si="11"/>
         <v>190244</v>
       </c>
       <c r="K14" s="10">
-        <f>+SUM(K11:K13)</f>
+        <f t="shared" si="11"/>
         <v>184975</v>
       </c>
-      <c r="L14" s="16"/>
-      <c r="M14" s="16"/>
-      <c r="N14" s="16"/>
-      <c r="O14" s="16"/>
       <c r="T14" s="10">
         <f>336.6*1000</f>
         <v>336600</v>
@@ -2760,67 +2753,67 @@
         <v>227600</v>
       </c>
       <c r="X14" s="10">
-        <f>+SUM(X11:X13)</f>
+        <f t="shared" ref="X14:AD14" si="12">+SUM(X11:X13)</f>
         <v>246322</v>
       </c>
       <c r="Y14" s="10">
-        <f>+SUM(Y11:Y13)</f>
+        <f t="shared" si="12"/>
         <v>328304</v>
       </c>
       <c r="Z14" s="10">
-        <f>+SUM(Z11:Z13)</f>
+        <f t="shared" si="12"/>
         <v>454793</v>
       </c>
       <c r="AA14" s="10">
-        <f>+SUM(AA11:AA13)</f>
+        <f t="shared" si="12"/>
         <v>461117</v>
       </c>
       <c r="AB14" s="10">
-        <f>+SUM(AB11:AB13)</f>
+        <f t="shared" si="12"/>
         <v>556624</v>
       </c>
       <c r="AC14" s="10">
-        <f>+SUM(AC11:AC13)</f>
+        <f t="shared" si="12"/>
         <v>707630</v>
       </c>
       <c r="AD14" s="10">
-        <f>+SUM(AD11:AD13)</f>
+        <f t="shared" si="12"/>
         <v>786414.42</v>
       </c>
       <c r="AE14" s="10">
-        <f t="shared" ref="AE14:AM14" si="11">+SUM(AE11:AE13)</f>
+        <f t="shared" ref="AE14:AM14" si="13">+SUM(AE11:AE13)</f>
         <v>862959.93299999996</v>
       </c>
       <c r="AF14" s="10">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>950773.06823400001</v>
       </c>
       <c r="AG14" s="10">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1051607.9005086599</v>
       </c>
       <c r="AH14" s="10">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1167495.5533000121</v>
       </c>
       <c r="AI14" s="10">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1300788.2412393887</v>
       </c>
       <c r="AJ14" s="10">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1454210.3366026322</v>
       </c>
       <c r="AK14" s="10">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1630917.581819853</v>
       </c>
       <c r="AL14" s="10">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>1834565.7493999037</v>
       </c>
       <c r="AM14" s="10">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>2069390.2587292739</v>
       </c>
     </row>
@@ -2876,39 +2869,39 @@
         <v>149674.68039173016</v>
       </c>
       <c r="AE15" s="3">
-        <f t="shared" ref="AE15:AM16" si="12">+AE$14*(AD15/AD$14)</f>
+        <f t="shared" ref="AE15:AM16" si="14">+AE$14*(AD15/AD$14)</f>
         <v>164243.23979542981</v>
       </c>
       <c r="AF15" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>180956.31450016977</v>
       </c>
       <c r="AG15" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>200147.74958736394</v>
       </c>
       <c r="AH15" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>222204.11955180767</v>
       </c>
       <c r="AI15" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>247573.11070774402</v>
       </c>
       <c r="AJ15" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>276773.24044153374</v>
       </c>
       <c r="AK15" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>310405.1268593726</v>
       </c>
       <c r="AL15" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>349164.55651849002</v>
       </c>
       <c r="AM15" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>393857.63753043074</v>
       </c>
     </row>
@@ -2964,39 +2957,39 @@
         <v>3173.9745114254624</v>
       </c>
       <c r="AE16" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>3482.9127773667024</v>
       </c>
       <c r="AF16" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>3837.3272513549509</v>
       </c>
       <c r="AG16" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>4244.2973924971138</v>
       </c>
       <c r="AH16" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>4712.0208304125526</v>
       </c>
       <c r="AI16" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>5249.9911210373975</v>
       </c>
       <c r="AJ16" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>5869.2038513589268</v>
       </c>
       <c r="AK16" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>6582.3956215501039</v>
       </c>
       <c r="AL16" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>7404.3211569409505</v>
       </c>
       <c r="AM16" s="3">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>8352.0746420174473</v>
       </c>
     </row>
@@ -3005,99 +2998,99 @@
         <v>21</v>
       </c>
       <c r="C17" s="3">
-        <f>+C14-SUM(C15:C16)</f>
+        <f t="shared" ref="C17:J17" si="15">+C14-SUM(C15:C16)</f>
         <v>97268</v>
       </c>
       <c r="D17" s="3">
-        <f>+D14-SUM(D15:D16)</f>
+        <f t="shared" si="15"/>
         <v>108359</v>
       </c>
       <c r="E17" s="3">
-        <f>+E14-SUM(E15:E16)</f>
+        <f t="shared" si="15"/>
         <v>120207</v>
       </c>
       <c r="F17" s="3">
-        <f>+F14-SUM(F15:F16)</f>
+        <f t="shared" si="15"/>
         <v>131887</v>
       </c>
       <c r="G17" s="3">
-        <f>+G14-SUM(G15:G16)</f>
+        <f t="shared" si="15"/>
         <v>135535</v>
       </c>
       <c r="H17" s="3">
-        <f>+H14-SUM(H15:H16)</f>
+        <f t="shared" si="15"/>
         <v>139160</v>
       </c>
       <c r="I17" s="3">
-        <f>+I14-SUM(I15:I16)</f>
+        <f t="shared" si="15"/>
         <v>143645</v>
       </c>
       <c r="J17" s="3">
-        <f>+J14-SUM(J15:J16)</f>
+        <f t="shared" si="15"/>
         <v>151754</v>
       </c>
       <c r="X17" s="3">
-        <f>+X14-SUM(X15:X16)</f>
+        <f t="shared" ref="X17:AD17" si="16">+X14-SUM(X15:X16)</f>
         <v>202926</v>
       </c>
       <c r="Y17" s="3">
-        <f>+Y14-SUM(Y15:Y16)</f>
+        <f t="shared" si="16"/>
         <v>274151</v>
       </c>
       <c r="Z17" s="3">
-        <f>+Z14-SUM(Z15:Z16)</f>
+        <f t="shared" si="16"/>
         <v>361149</v>
       </c>
       <c r="AA17" s="3">
-        <f>+AA14-SUM(AA15:AA16)</f>
+        <f t="shared" si="16"/>
         <v>371219</v>
       </c>
       <c r="AB17" s="3">
-        <f>+AB14-SUM(AB15:AB16)</f>
+        <f t="shared" si="16"/>
         <v>457721</v>
       </c>
       <c r="AC17" s="3">
-        <f>+AC14-SUM(AC15:AC16)</f>
+        <f t="shared" si="16"/>
         <v>570094</v>
       </c>
       <c r="AD17" s="3">
-        <f>+AD14-SUM(AD15:AD16)</f>
+        <f t="shared" si="16"/>
         <v>633565.76509684441</v>
       </c>
       <c r="AE17" s="3">
-        <f t="shared" ref="AE17:AM17" si="13">+AE14-SUM(AE15:AE16)</f>
+        <f t="shared" ref="AE17:AM17" si="17">+AE14-SUM(AE15:AE16)</f>
         <v>695233.78042720351</v>
       </c>
       <c r="AF17" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>765979.42648247525</v>
       </c>
       <c r="AG17" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>847215.85352879879</v>
       </c>
       <c r="AH17" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>940579.41291779187</v>
       </c>
       <c r="AI17" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>1047965.1394106073</v>
       </c>
       <c r="AJ17" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>1171567.8923097395</v>
       </c>
       <c r="AK17" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>1313930.0593389303</v>
       </c>
       <c r="AL17" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>1477996.8717244728</v>
       </c>
       <c r="AM17" s="3">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>1667180.5465568257</v>
       </c>
     </row>
@@ -3153,39 +3146,39 @@
         <v>202154.17072034822</v>
       </c>
       <c r="AE18" s="3">
-        <f t="shared" ref="AE18:AM18" si="14">+AE$14*(AD18/AD$14)</f>
+        <f t="shared" ref="AE18:AM18" si="18">+AE$14*(AD18/AD$14)</f>
         <v>221830.81233492927</v>
       </c>
       <c r="AF18" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>244403.88714144548</v>
       </c>
       <c r="AG18" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>270324.29421919119</v>
       </c>
       <c r="AH18" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>300114.15024289361</v>
       </c>
       <c r="AI18" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>334378.11095901427</v>
       </c>
       <c r="AJ18" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>373816.49823875754</v>
       </c>
       <c r="AK18" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>419240.52113137505</v>
       </c>
       <c r="AL18" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>471589.92545163614</v>
       </c>
       <c r="AM18" s="3">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>531953.45992025826</v>
       </c>
     </row>
@@ -3241,39 +3234,39 @@
         <v>123998.38238333593</v>
       </c>
       <c r="AE19" s="3">
-        <f t="shared" ref="AE19:AM19" si="15">+AE$14*(AD19/AD$14)</f>
+        <f t="shared" ref="AE19:AM19" si="19">+AE$14*(AD19/AD$14)</f>
         <v>136067.74371409917</v>
       </c>
       <c r="AF19" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>149913.73438276612</v>
       </c>
       <c r="AG19" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>165812.92922453012</v>
       </c>
       <c r="AH19" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>184085.58689569714</v>
       </c>
       <c r="AI19" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>205102.59430002409</v>
       </c>
       <c r="AJ19" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>229293.51852913995</v>
       </c>
       <c r="AK19" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>257155.94323181879</v>
       </c>
       <c r="AL19" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>289266.29461023933</v>
       </c>
       <c r="AM19" s="3">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>326292.39504822786</v>
       </c>
     </row>
@@ -3282,99 +3275,99 @@
         <v>24</v>
       </c>
       <c r="C20" s="3">
-        <f>+C17-SUM(C18:C19)</f>
+        <f t="shared" ref="C20:J20" si="20">+C17-SUM(C18:C19)</f>
         <v>34082</v>
       </c>
       <c r="D20" s="3">
-        <f>+D17-SUM(D18:D19)</f>
+        <f t="shared" si="20"/>
         <v>43432</v>
       </c>
       <c r="E20" s="3">
-        <f>+E17-SUM(E18:E19)</f>
+        <f t="shared" si="20"/>
         <v>53041</v>
       </c>
       <c r="F20" s="3">
-        <f>+F17-SUM(F18:F19)</f>
+        <f t="shared" si="20"/>
         <v>60191</v>
       </c>
       <c r="G20" s="3">
-        <f>+G17-SUM(G18:G19)</f>
+        <f t="shared" si="20"/>
         <v>64857</v>
       </c>
       <c r="H20" s="3">
-        <f>+H17-SUM(H18:H19)</f>
+        <f t="shared" si="20"/>
         <v>74233</v>
       </c>
       <c r="I20" s="3">
-        <f>+I17-SUM(I18:I19)</f>
+        <f t="shared" si="20"/>
         <v>64979</v>
       </c>
       <c r="J20" s="3">
-        <f>+J17-SUM(J18:J19)</f>
+        <f t="shared" si="20"/>
         <v>72547</v>
       </c>
       <c r="X20" s="3">
-        <f>+X17-SUM(X18:X19)</f>
+        <f t="shared" ref="X20:AD20" si="21">+X17-SUM(X18:X19)</f>
         <v>-23352</v>
       </c>
       <c r="Y20" s="3">
-        <f>+Y17-SUM(Y18:Y19)</f>
+        <f t="shared" si="21"/>
         <v>47416</v>
       </c>
       <c r="Z20" s="3">
-        <f>+Z17-SUM(Z18:Z19)</f>
+        <f t="shared" si="21"/>
         <v>95662</v>
       </c>
       <c r="AA20" s="3">
-        <f>+AA17-SUM(AA18:AA19)</f>
+        <f t="shared" si="21"/>
         <v>106243</v>
       </c>
       <c r="AB20" s="3">
-        <f>+AB17-SUM(AB18:AB19)</f>
+        <f t="shared" si="21"/>
         <v>190746</v>
       </c>
       <c r="AC20" s="3">
-        <f>+AC17-SUM(AC18:AC19)</f>
+        <f t="shared" si="21"/>
         <v>276616</v>
       </c>
       <c r="AD20" s="3">
-        <f>+AD17-SUM(AD18:AD19)</f>
+        <f t="shared" si="21"/>
         <v>307413.21199316025</v>
       </c>
       <c r="AE20" s="3">
-        <f t="shared" ref="AE20:AM20" si="16">+AE17-SUM(AE18:AE19)</f>
+        <f t="shared" ref="AE20:AM20" si="22">+AE17-SUM(AE18:AE19)</f>
         <v>337335.2243781751</v>
       </c>
       <c r="AF20" s="3">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>371661.80495826364</v>
       </c>
       <c r="AG20" s="3">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>411078.63008507749</v>
       </c>
       <c r="AH20" s="3">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>456379.67577920109</v>
       </c>
       <c r="AI20" s="3">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>508484.43415156892</v>
       </c>
       <c r="AJ20" s="3">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>568457.87554184196</v>
       </c>
       <c r="AK20" s="3">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>637533.59497573646</v>
       </c>
       <c r="AL20" s="3">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>717140.65166259743</v>
       </c>
       <c r="AM20" s="3">
-        <f t="shared" si="16"/>
+        <f t="shared" si="22"/>
         <v>808934.69158833963</v>
       </c>
     </row>
@@ -3443,39 +3436,39 @@
         <v>20921</v>
       </c>
       <c r="AE21" s="3">
-        <f t="shared" ref="AE21:AM21" si="17">+AD21</f>
+        <f t="shared" ref="AE21:AM21" si="23">+AD21</f>
         <v>20921</v>
       </c>
       <c r="AF21" s="3">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>20921</v>
       </c>
       <c r="AG21" s="3">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>20921</v>
       </c>
       <c r="AH21" s="3">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>20921</v>
       </c>
       <c r="AI21" s="3">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>20921</v>
       </c>
       <c r="AJ21" s="3">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>20921</v>
       </c>
       <c r="AK21" s="3">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>20921</v>
       </c>
       <c r="AL21" s="3">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>20921</v>
       </c>
       <c r="AM21" s="3">
-        <f t="shared" si="17"/>
+        <f t="shared" si="23"/>
         <v>20921</v>
       </c>
     </row>
@@ -3484,99 +3477,99 @@
         <v>26</v>
       </c>
       <c r="C22" s="3">
-        <f>+C20+C21</f>
+        <f t="shared" ref="C22:J22" si="24">+C20+C21</f>
         <v>38303</v>
       </c>
       <c r="D22" s="3">
-        <f>+D20+D21</f>
+        <f t="shared" si="24"/>
         <v>47461</v>
       </c>
       <c r="E22" s="3">
-        <f>+E20+E21</f>
+        <f t="shared" si="24"/>
         <v>57381</v>
       </c>
       <c r="F22" s="3">
-        <f>+F20+F21</f>
+        <f t="shared" si="24"/>
         <v>64635</v>
       </c>
       <c r="G22" s="3">
-        <f>+G20+G21</f>
+        <f t="shared" si="24"/>
         <v>69336</v>
       </c>
       <c r="H22" s="3">
-        <f>+H20+H21</f>
+        <f t="shared" si="24"/>
         <v>78262</v>
       </c>
       <c r="I22" s="3">
-        <f>+I20+I21</f>
+        <f t="shared" si="24"/>
         <v>71012</v>
       </c>
       <c r="J22" s="3">
-        <f>+J20+J21</f>
+        <f t="shared" si="24"/>
         <v>78927</v>
       </c>
       <c r="X22" s="3">
-        <f>+X20+X21</f>
+        <f t="shared" ref="X22:AD22" si="25">+X20+X21</f>
         <v>-15837</v>
       </c>
       <c r="Y22" s="3">
-        <f>+Y20+Y21</f>
+        <f t="shared" si="25"/>
         <v>46421</v>
       </c>
       <c r="Z22" s="3">
-        <f>+Z20+Z21</f>
+        <f t="shared" si="25"/>
         <v>101559</v>
       </c>
       <c r="AA22" s="3">
-        <f>+AA20+AA21</f>
+        <f t="shared" si="25"/>
         <v>116080</v>
       </c>
       <c r="AB22" s="3">
-        <f>+AB20+AB21</f>
+        <f t="shared" si="25"/>
         <v>207780</v>
       </c>
       <c r="AC22" s="3">
-        <f>+AC20+AC21</f>
+        <f t="shared" si="25"/>
         <v>297537</v>
       </c>
       <c r="AD22" s="3">
-        <f>+AD20+AD21</f>
+        <f t="shared" si="25"/>
         <v>328334.21199316025</v>
       </c>
       <c r="AE22" s="3">
-        <f t="shared" ref="AE22:AM22" si="18">+AE20+AE21</f>
+        <f t="shared" ref="AE22:AM22" si="26">+AE20+AE21</f>
         <v>358256.2243781751</v>
       </c>
       <c r="AF22" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="26"/>
         <v>392582.80495826364</v>
       </c>
       <c r="AG22" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="26"/>
         <v>431999.63008507749</v>
       </c>
       <c r="AH22" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="26"/>
         <v>477300.67577920109</v>
       </c>
       <c r="AI22" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="26"/>
         <v>529405.43415156892</v>
       </c>
       <c r="AJ22" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="26"/>
         <v>589378.87554184196</v>
       </c>
       <c r="AK22" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="26"/>
         <v>658454.59497573646</v>
       </c>
       <c r="AL22" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="26"/>
         <v>738061.65166259743</v>
       </c>
       <c r="AM22" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="26"/>
         <v>829855.69158833963</v>
       </c>
     </row>
@@ -3631,39 +3624,39 @@
         <v>14750.580303332268</v>
       </c>
       <c r="AE23" s="3">
-        <f t="shared" ref="AE23:AM23" si="19">+AE$22*(AD23/AD$22)</f>
+        <f t="shared" ref="AE23:AM23" si="27">+AE$22*(AD23/AD$22)</f>
         <v>16094.841822237457</v>
       </c>
       <c r="AF23" s="3">
-        <f t="shared" si="19"/>
+        <f t="shared" si="27"/>
         <v>17636.980791891798</v>
       </c>
       <c r="AG23" s="3">
-        <f t="shared" si="19"/>
+        <f t="shared" si="27"/>
         <v>19407.801568703155</v>
       </c>
       <c r="AH23" s="3">
-        <f t="shared" si="19"/>
+        <f t="shared" si="27"/>
         <v>21442.973926404382</v>
       </c>
       <c r="AI23" s="3">
-        <f t="shared" si="19"/>
+        <f t="shared" si="27"/>
         <v>23783.806512480871</v>
       </c>
       <c r="AJ23" s="3">
-        <f t="shared" si="19"/>
+        <f t="shared" si="27"/>
         <v>26478.143657319262</v>
       </c>
       <c r="AK23" s="3">
-        <f t="shared" si="19"/>
+        <f t="shared" si="27"/>
         <v>29581.405240493346</v>
       </c>
       <c r="AL23" s="3">
-        <f t="shared" si="19"/>
+        <f t="shared" si="27"/>
         <v>33157.792468748223</v>
       </c>
       <c r="AM23" s="3">
-        <f t="shared" si="19"/>
+        <f t="shared" si="27"/>
         <v>37281.686074207028</v>
       </c>
     </row>
@@ -3672,108 +3665,103 @@
         <v>28</v>
       </c>
       <c r="C24" s="10">
-        <f>+C22-C23</f>
+        <f t="shared" ref="C24:J24" si="28">+C22-C23</f>
         <v>36849</v>
       </c>
       <c r="D24" s="10">
-        <f>+D22-D23</f>
+        <f t="shared" si="28"/>
         <v>39166</v>
       </c>
       <c r="E24" s="10">
-        <f>+E22-E23</f>
+        <f t="shared" si="28"/>
         <v>47011</v>
       </c>
       <c r="F24" s="10">
-        <f>+F22-F23</f>
+        <f t="shared" si="28"/>
         <v>64532</v>
       </c>
       <c r="G24" s="10">
-        <f>+G22-G23</f>
+        <f t="shared" si="28"/>
         <v>62016</v>
       </c>
       <c r="H24" s="10">
-        <f>+H22-H23</f>
+        <f t="shared" si="28"/>
         <v>69967</v>
       </c>
       <c r="I24" s="10">
-        <f>+I22-I23</f>
+        <f t="shared" si="28"/>
         <v>50101</v>
       </c>
       <c r="J24" s="10">
-        <f>+J22-J23</f>
+        <f t="shared" si="28"/>
         <v>65560</v>
       </c>
-      <c r="K24" s="16"/>
-      <c r="L24" s="16"/>
-      <c r="M24" s="16"/>
-      <c r="N24" s="16"/>
-      <c r="O24" s="16"/>
       <c r="T24" s="10"/>
       <c r="U24" s="10"/>
       <c r="V24" s="10"/>
       <c r="W24" s="10"/>
       <c r="X24" s="10">
-        <f>+X22-X23</f>
+        <f t="shared" ref="X24:AD24" si="29">+X22-X23</f>
         <v>-19769</v>
       </c>
       <c r="Y24" s="10">
-        <f>+Y22-Y23</f>
+        <f t="shared" si="29"/>
         <v>41469</v>
       </c>
       <c r="Z24" s="10">
-        <f>+Z22-Z23</f>
+        <f t="shared" si="29"/>
         <v>95074</v>
       </c>
       <c r="AA24" s="10">
-        <f>+AA22-AA23</f>
+        <f t="shared" si="29"/>
         <v>262824</v>
       </c>
       <c r="AB24" s="10">
-        <f>+AB22-AB23</f>
+        <f t="shared" si="29"/>
         <v>187558</v>
       </c>
       <c r="AC24" s="10">
-        <f>+AC22-AC23</f>
+        <f t="shared" si="29"/>
         <v>284170</v>
       </c>
       <c r="AD24" s="10">
-        <f>+AD22-AD23</f>
+        <f t="shared" si="29"/>
         <v>313583.63168982801</v>
       </c>
       <c r="AE24" s="10">
-        <f t="shared" ref="AE24:AM24" si="20">+AE22-AE23</f>
+        <f t="shared" ref="AE24:AM24" si="30">+AE22-AE23</f>
         <v>342161.38255593763</v>
       </c>
       <c r="AF24" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="30"/>
         <v>374945.82416637184</v>
       </c>
       <c r="AG24" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="30"/>
         <v>412591.82851637434</v>
       </c>
       <c r="AH24" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="30"/>
         <v>455857.70185279672</v>
       </c>
       <c r="AI24" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="30"/>
         <v>505621.62763908802</v>
       </c>
       <c r="AJ24" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="30"/>
         <v>562900.73188452271</v>
       </c>
       <c r="AK24" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="30"/>
         <v>628873.1897352431</v>
       </c>
       <c r="AL24" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="30"/>
         <v>704903.85919384926</v>
       </c>
       <c r="AM24" s="10">
-        <f t="shared" si="20"/>
+        <f t="shared" si="30"/>
         <v>792574.00551413256</v>
       </c>
       <c r="AN24" s="7">
@@ -3781,818 +3769,818 @@
         <v>800499.74556927395</v>
       </c>
       <c r="AO24" s="7">
-        <f t="shared" ref="AO24:CZ24" si="21">+AN24*(1+$AP$32)</f>
+        <f t="shared" ref="AO24:CZ24" si="31">+AN24*(1+$AP$32)</f>
         <v>808504.74302496668</v>
       </c>
       <c r="AP24" s="7">
-        <f t="shared" si="21"/>
+        <f t="shared" si="31"/>
         <v>816589.79045521631</v>
       </c>
       <c r="AQ24" s="7">
-        <f t="shared" si="21"/>
+        <f t="shared" si="31"/>
         <v>824755.68835976848</v>
       </c>
       <c r="AR24" s="7">
-        <f t="shared" si="21"/>
+        <f t="shared" si="31"/>
         <v>833003.24524336623</v>
       </c>
       <c r="AS24" s="7">
-        <f t="shared" si="21"/>
+        <f t="shared" si="31"/>
         <v>841333.27769579994</v>
       </c>
       <c r="AT24" s="7">
-        <f t="shared" si="21"/>
+        <f t="shared" si="31"/>
         <v>849746.61047275795</v>
       </c>
       <c r="AU24" s="7">
-        <f t="shared" si="21"/>
+        <f t="shared" si="31"/>
         <v>858244.07657748554</v>
       </c>
       <c r="AV24" s="7">
-        <f t="shared" si="21"/>
+        <f t="shared" si="31"/>
         <v>866826.51734326035</v>
       </c>
       <c r="AW24" s="7">
-        <f t="shared" si="21"/>
+        <f t="shared" si="31"/>
         <v>875494.782516693</v>
       </c>
       <c r="AX24" s="7">
-        <f t="shared" si="21"/>
+        <f t="shared" si="31"/>
         <v>884249.73034185998</v>
       </c>
       <c r="AY24" s="7">
-        <f t="shared" si="21"/>
+        <f t="shared" si="31"/>
         <v>893092.22764527856</v>
       </c>
       <c r="AZ24" s="7">
-        <f t="shared" si="21"/>
+        <f t="shared" si="31"/>
         <v>902023.14992173132</v>
       </c>
       <c r="BA24" s="7">
-        <f t="shared" si="21"/>
+        <f t="shared" si="31"/>
         <v>911043.38142094866</v>
       </c>
       <c r="BB24" s="7">
-        <f t="shared" si="21"/>
+        <f t="shared" si="31"/>
         <v>920153.8152351582</v>
       </c>
       <c r="BC24" s="7">
-        <f t="shared" si="21"/>
+        <f t="shared" si="31"/>
         <v>929355.35338750982</v>
       </c>
       <c r="BD24" s="7">
-        <f t="shared" si="21"/>
+        <f t="shared" si="31"/>
         <v>938648.90692138497</v>
       </c>
       <c r="BE24" s="7">
-        <f t="shared" si="21"/>
+        <f t="shared" si="31"/>
         <v>948035.39599059883</v>
       </c>
       <c r="BF24" s="7">
-        <f t="shared" si="21"/>
+        <f t="shared" si="31"/>
         <v>957515.74995050486</v>
       </c>
       <c r="BG24" s="7">
-        <f t="shared" si="21"/>
+        <f t="shared" si="31"/>
         <v>967090.90745000995</v>
       </c>
       <c r="BH24" s="7">
-        <f t="shared" si="21"/>
+        <f t="shared" si="31"/>
         <v>976761.81652451004</v>
       </c>
       <c r="BI24" s="7">
-        <f t="shared" si="21"/>
+        <f t="shared" si="31"/>
         <v>986529.4346897552</v>
       </c>
       <c r="BJ24" s="7">
-        <f t="shared" si="21"/>
+        <f t="shared" si="31"/>
         <v>996394.72903665272</v>
       </c>
       <c r="BK24" s="7">
-        <f t="shared" si="21"/>
+        <f t="shared" si="31"/>
         <v>1006358.6763270192</v>
       </c>
       <c r="BL24" s="7">
-        <f t="shared" si="21"/>
+        <f t="shared" si="31"/>
         <v>1016422.2630902894</v>
       </c>
       <c r="BM24" s="7">
-        <f t="shared" si="21"/>
+        <f t="shared" si="31"/>
         <v>1026586.4857211923</v>
       </c>
       <c r="BN24" s="7">
-        <f t="shared" si="21"/>
+        <f t="shared" si="31"/>
         <v>1036852.3505784043</v>
       </c>
       <c r="BO24" s="7">
-        <f t="shared" si="21"/>
+        <f t="shared" si="31"/>
         <v>1047220.8740841884</v>
       </c>
       <c r="BP24" s="7">
-        <f t="shared" si="21"/>
+        <f t="shared" si="31"/>
         <v>1057693.0828250302</v>
       </c>
       <c r="BQ24" s="7">
-        <f t="shared" si="21"/>
+        <f t="shared" si="31"/>
         <v>1068270.0136532804</v>
       </c>
       <c r="BR24" s="7">
-        <f t="shared" si="21"/>
+        <f t="shared" si="31"/>
         <v>1078952.7137898132</v>
       </c>
       <c r="BS24" s="7">
-        <f t="shared" si="21"/>
+        <f t="shared" si="31"/>
         <v>1089742.2409277114</v>
       </c>
       <c r="BT24" s="7">
-        <f t="shared" si="21"/>
+        <f t="shared" si="31"/>
         <v>1100639.6633369885</v>
       </c>
       <c r="BU24" s="7">
-        <f t="shared" si="21"/>
+        <f t="shared" si="31"/>
         <v>1111646.0599703584</v>
       </c>
       <c r="BV24" s="7">
-        <f t="shared" si="21"/>
+        <f t="shared" si="31"/>
         <v>1122762.5205700619</v>
       </c>
       <c r="BW24" s="7">
-        <f t="shared" si="21"/>
+        <f t="shared" si="31"/>
         <v>1133990.1457757624</v>
       </c>
       <c r="BX24" s="7">
-        <f t="shared" si="21"/>
+        <f t="shared" si="31"/>
         <v>1145330.0472335201</v>
       </c>
       <c r="BY24" s="7">
-        <f t="shared" si="21"/>
+        <f t="shared" si="31"/>
         <v>1156783.3477058553</v>
       </c>
       <c r="BZ24" s="7">
-        <f t="shared" si="21"/>
+        <f t="shared" si="31"/>
         <v>1168351.1811829137</v>
       </c>
       <c r="CA24" s="7">
-        <f t="shared" si="21"/>
+        <f t="shared" si="31"/>
         <v>1180034.6929947429</v>
       </c>
       <c r="CB24" s="7">
-        <f t="shared" si="21"/>
+        <f t="shared" si="31"/>
         <v>1191835.0399246903</v>
       </c>
       <c r="CC24" s="7">
-        <f t="shared" si="21"/>
+        <f t="shared" si="31"/>
         <v>1203753.3903239372</v>
       </c>
       <c r="CD24" s="7">
-        <f t="shared" si="21"/>
+        <f t="shared" si="31"/>
         <v>1215790.9242271765</v>
       </c>
       <c r="CE24" s="7">
-        <f t="shared" si="21"/>
+        <f t="shared" si="31"/>
         <v>1227948.8334694481</v>
       </c>
       <c r="CF24" s="7">
-        <f t="shared" si="21"/>
+        <f t="shared" si="31"/>
         <v>1240228.3218041426</v>
       </c>
       <c r="CG24" s="7">
-        <f t="shared" si="21"/>
+        <f t="shared" si="31"/>
         <v>1252630.6050221841</v>
       </c>
       <c r="CH24" s="7">
-        <f t="shared" si="21"/>
+        <f t="shared" si="31"/>
         <v>1265156.911072406</v>
       </c>
       <c r="CI24" s="7">
-        <f t="shared" si="21"/>
+        <f t="shared" si="31"/>
         <v>1277808.4801831301</v>
       </c>
       <c r="CJ24" s="7">
-        <f t="shared" si="21"/>
+        <f t="shared" si="31"/>
         <v>1290586.5649849614</v>
       </c>
       <c r="CK24" s="7">
-        <f t="shared" si="21"/>
+        <f t="shared" si="31"/>
         <v>1303492.4306348111</v>
       </c>
       <c r="CL24" s="7">
-        <f t="shared" si="21"/>
+        <f t="shared" si="31"/>
         <v>1316527.3549411593</v>
       </c>
       <c r="CM24" s="7">
-        <f t="shared" si="21"/>
+        <f t="shared" si="31"/>
         <v>1329692.6284905709</v>
       </c>
       <c r="CN24" s="7">
-        <f t="shared" si="21"/>
+        <f t="shared" si="31"/>
         <v>1342989.5547754767</v>
       </c>
       <c r="CO24" s="7">
-        <f t="shared" si="21"/>
+        <f t="shared" si="31"/>
         <v>1356419.4503232315</v>
       </c>
       <c r="CP24" s="7">
-        <f t="shared" si="21"/>
+        <f t="shared" si="31"/>
         <v>1369983.6448264639</v>
       </c>
       <c r="CQ24" s="7">
-        <f t="shared" si="21"/>
+        <f t="shared" si="31"/>
         <v>1383683.4812747284</v>
       </c>
       <c r="CR24" s="7">
-        <f t="shared" si="21"/>
+        <f t="shared" si="31"/>
         <v>1397520.3160874757</v>
       </c>
       <c r="CS24" s="7">
-        <f t="shared" si="21"/>
+        <f t="shared" si="31"/>
         <v>1411495.5192483505</v>
       </c>
       <c r="CT24" s="7">
-        <f t="shared" si="21"/>
+        <f t="shared" si="31"/>
         <v>1425610.474440834</v>
       </c>
       <c r="CU24" s="7">
-        <f t="shared" si="21"/>
+        <f t="shared" si="31"/>
         <v>1439866.5791852423</v>
       </c>
       <c r="CV24" s="7">
-        <f t="shared" si="21"/>
+        <f t="shared" si="31"/>
         <v>1454265.2449770947</v>
       </c>
       <c r="CW24" s="7">
-        <f t="shared" si="21"/>
+        <f t="shared" si="31"/>
         <v>1468807.8974268658</v>
       </c>
       <c r="CX24" s="7">
-        <f t="shared" si="21"/>
+        <f t="shared" si="31"/>
         <v>1483495.9764011344</v>
       </c>
       <c r="CY24" s="7">
-        <f t="shared" si="21"/>
+        <f t="shared" si="31"/>
         <v>1498330.9361651458</v>
       </c>
       <c r="CZ24" s="7">
-        <f t="shared" si="21"/>
+        <f t="shared" si="31"/>
         <v>1513314.2455267974</v>
       </c>
       <c r="DA24" s="7">
-        <f t="shared" ref="DA24:FL24" si="22">+CZ24*(1+$AP$32)</f>
+        <f t="shared" ref="DA24:FL24" si="32">+CZ24*(1+$AP$32)</f>
         <v>1528447.3879820653</v>
       </c>
       <c r="DB24" s="7">
-        <f t="shared" si="22"/>
+        <f t="shared" si="32"/>
         <v>1543731.861861886</v>
       </c>
       <c r="DC24" s="7">
-        <f t="shared" si="22"/>
+        <f t="shared" si="32"/>
         <v>1559169.1804805049</v>
       </c>
       <c r="DD24" s="7">
-        <f t="shared" si="22"/>
+        <f t="shared" si="32"/>
         <v>1574760.8722853099</v>
       </c>
       <c r="DE24" s="7">
-        <f t="shared" si="22"/>
+        <f t="shared" si="32"/>
         <v>1590508.481008163</v>
       </c>
       <c r="DF24" s="7">
-        <f t="shared" si="22"/>
+        <f t="shared" si="32"/>
         <v>1606413.5658182446</v>
       </c>
       <c r="DG24" s="7">
-        <f t="shared" si="22"/>
+        <f t="shared" si="32"/>
         <v>1622477.701476427</v>
       </c>
       <c r="DH24" s="7">
-        <f t="shared" si="22"/>
+        <f t="shared" si="32"/>
         <v>1638702.4784911913</v>
       </c>
       <c r="DI24" s="7">
-        <f t="shared" si="22"/>
+        <f t="shared" si="32"/>
         <v>1655089.5032761032</v>
       </c>
       <c r="DJ24" s="7">
-        <f t="shared" si="22"/>
+        <f t="shared" si="32"/>
         <v>1671640.3983088643</v>
       </c>
       <c r="DK24" s="7">
-        <f t="shared" si="22"/>
+        <f t="shared" si="32"/>
         <v>1688356.802291953</v>
       </c>
       <c r="DL24" s="7">
-        <f t="shared" si="22"/>
+        <f t="shared" si="32"/>
         <v>1705240.3703148726</v>
       </c>
       <c r="DM24" s="7">
-        <f t="shared" si="22"/>
+        <f t="shared" si="32"/>
         <v>1722292.7740180213</v>
       </c>
       <c r="DN24" s="7">
-        <f t="shared" si="22"/>
+        <f t="shared" si="32"/>
         <v>1739515.7017582015</v>
       </c>
       <c r="DO24" s="7">
-        <f t="shared" si="22"/>
+        <f t="shared" si="32"/>
         <v>1756910.8587757836</v>
       </c>
       <c r="DP24" s="7">
-        <f t="shared" si="22"/>
+        <f t="shared" si="32"/>
         <v>1774479.9673635415</v>
       </c>
       <c r="DQ24" s="7">
-        <f t="shared" si="22"/>
+        <f t="shared" si="32"/>
         <v>1792224.767037177</v>
       </c>
       <c r="DR24" s="7">
-        <f t="shared" si="22"/>
+        <f t="shared" si="32"/>
         <v>1810147.0147075488</v>
       </c>
       <c r="DS24" s="7">
-        <f t="shared" si="22"/>
+        <f t="shared" si="32"/>
         <v>1828248.4848546244</v>
       </c>
       <c r="DT24" s="7">
-        <f t="shared" si="22"/>
+        <f t="shared" si="32"/>
         <v>1846530.9697031707</v>
       </c>
       <c r="DU24" s="7">
-        <f t="shared" si="22"/>
+        <f t="shared" si="32"/>
         <v>1864996.2794002024</v>
       </c>
       <c r="DV24" s="7">
-        <f t="shared" si="22"/>
+        <f t="shared" si="32"/>
         <v>1883646.2421942046</v>
       </c>
       <c r="DW24" s="7">
-        <f t="shared" si="22"/>
+        <f t="shared" si="32"/>
         <v>1902482.7046161466</v>
       </c>
       <c r="DX24" s="7">
-        <f t="shared" si="22"/>
+        <f t="shared" si="32"/>
         <v>1921507.5316623081</v>
       </c>
       <c r="DY24" s="7">
-        <f t="shared" si="22"/>
+        <f t="shared" si="32"/>
         <v>1940722.6069789312</v>
       </c>
       <c r="DZ24" s="7">
-        <f t="shared" si="22"/>
+        <f t="shared" si="32"/>
         <v>1960129.8330487206</v>
       </c>
       <c r="EA24" s="7">
-        <f t="shared" si="22"/>
+        <f t="shared" si="32"/>
         <v>1979731.1313792078</v>
       </c>
       <c r="EB24" s="7">
-        <f t="shared" si="22"/>
+        <f t="shared" si="32"/>
         <v>1999528.442693</v>
       </c>
       <c r="EC24" s="7">
-        <f t="shared" si="22"/>
+        <f t="shared" si="32"/>
         <v>2019523.7271199301</v>
       </c>
       <c r="ED24" s="7">
-        <f t="shared" si="22"/>
+        <f t="shared" si="32"/>
         <v>2039718.9643911293</v>
       </c>
       <c r="EE24" s="7">
-        <f t="shared" si="22"/>
+        <f t="shared" si="32"/>
         <v>2060116.1540350406</v>
       </c>
       <c r="EF24" s="7">
-        <f t="shared" si="22"/>
+        <f t="shared" si="32"/>
         <v>2080717.3155753911</v>
       </c>
       <c r="EG24" s="7">
-        <f t="shared" si="22"/>
+        <f t="shared" si="32"/>
         <v>2101524.4887311449</v>
       </c>
       <c r="EH24" s="7">
-        <f t="shared" si="22"/>
+        <f t="shared" si="32"/>
         <v>2122539.7336184564</v>
       </c>
       <c r="EI24" s="7">
-        <f t="shared" si="22"/>
+        <f t="shared" si="32"/>
         <v>2143765.1309546409</v>
       </c>
       <c r="EJ24" s="7">
-        <f t="shared" si="22"/>
+        <f t="shared" si="32"/>
         <v>2165202.7822641875</v>
       </c>
       <c r="EK24" s="7">
-        <f t="shared" si="22"/>
+        <f t="shared" si="32"/>
         <v>2186854.8100868296</v>
       </c>
       <c r="EL24" s="7">
-        <f t="shared" si="22"/>
+        <f t="shared" si="32"/>
         <v>2208723.3581876978</v>
       </c>
       <c r="EM24" s="7">
-        <f t="shared" si="22"/>
+        <f t="shared" si="32"/>
         <v>2230810.5917695747</v>
       </c>
       <c r="EN24" s="7">
-        <f t="shared" si="22"/>
+        <f t="shared" si="32"/>
         <v>2253118.6976872706</v>
       </c>
       <c r="EO24" s="7">
-        <f t="shared" si="22"/>
+        <f t="shared" si="32"/>
         <v>2275649.8846641434</v>
       </c>
       <c r="EP24" s="7">
-        <f t="shared" si="22"/>
+        <f t="shared" si="32"/>
         <v>2298406.3835107847</v>
       </c>
       <c r="EQ24" s="7">
-        <f t="shared" si="22"/>
+        <f t="shared" si="32"/>
         <v>2321390.4473458924</v>
       </c>
       <c r="ER24" s="7">
-        <f t="shared" si="22"/>
+        <f t="shared" si="32"/>
         <v>2344604.3518193513</v>
       </c>
       <c r="ES24" s="7">
-        <f t="shared" si="22"/>
+        <f t="shared" si="32"/>
         <v>2368050.3953375448</v>
       </c>
       <c r="ET24" s="7">
-        <f t="shared" si="22"/>
+        <f t="shared" si="32"/>
         <v>2391730.8992909202</v>
       </c>
       <c r="EU24" s="7">
-        <f t="shared" si="22"/>
+        <f t="shared" si="32"/>
         <v>2415648.2082838295</v>
       </c>
       <c r="EV24" s="7">
-        <f t="shared" si="22"/>
+        <f t="shared" si="32"/>
         <v>2439804.6903666677</v>
       </c>
       <c r="EW24" s="7">
-        <f t="shared" si="22"/>
+        <f t="shared" si="32"/>
         <v>2464202.7372703343</v>
       </c>
       <c r="EX24" s="7">
-        <f t="shared" si="22"/>
+        <f t="shared" si="32"/>
         <v>2488844.7646430377</v>
       </c>
       <c r="EY24" s="7">
-        <f t="shared" si="22"/>
+        <f t="shared" si="32"/>
         <v>2513733.2122894679</v>
       </c>
       <c r="EZ24" s="7">
-        <f t="shared" si="22"/>
+        <f t="shared" si="32"/>
         <v>2538870.5444123624</v>
       </c>
       <c r="FA24" s="7">
-        <f t="shared" si="22"/>
+        <f t="shared" si="32"/>
         <v>2564259.249856486</v>
       </c>
       <c r="FB24" s="7">
-        <f t="shared" si="22"/>
+        <f t="shared" si="32"/>
         <v>2589901.8423550511</v>
       </c>
       <c r="FC24" s="7">
-        <f t="shared" si="22"/>
+        <f t="shared" si="32"/>
         <v>2615800.8607786018</v>
       </c>
       <c r="FD24" s="7">
-        <f t="shared" si="22"/>
+        <f t="shared" si="32"/>
         <v>2641958.869386388</v>
       </c>
       <c r="FE24" s="7">
-        <f t="shared" si="22"/>
+        <f t="shared" si="32"/>
         <v>2668378.4580802517</v>
       </c>
       <c r="FF24" s="7">
-        <f t="shared" si="22"/>
+        <f t="shared" si="32"/>
         <v>2695062.2426610542</v>
       </c>
       <c r="FG24" s="7">
-        <f t="shared" si="22"/>
+        <f t="shared" si="32"/>
         <v>2722012.8650876647</v>
       </c>
       <c r="FH24" s="7">
-        <f t="shared" si="22"/>
+        <f t="shared" si="32"/>
         <v>2749232.9937385414</v>
       </c>
       <c r="FI24" s="7">
-        <f t="shared" si="22"/>
+        <f t="shared" si="32"/>
         <v>2776725.3236759268</v>
       </c>
       <c r="FJ24" s="7">
-        <f t="shared" si="22"/>
+        <f t="shared" si="32"/>
         <v>2804492.5769126862</v>
       </c>
       <c r="FK24" s="7">
-        <f t="shared" si="22"/>
+        <f t="shared" si="32"/>
         <v>2832537.5026818132</v>
       </c>
       <c r="FL24" s="7">
-        <f t="shared" si="22"/>
+        <f t="shared" si="32"/>
         <v>2860862.8777086316</v>
       </c>
       <c r="FM24" s="7">
-        <f t="shared" ref="FM24:GE24" si="23">+FL24*(1+$AP$32)</f>
+        <f t="shared" ref="FM24:GE24" si="33">+FL24*(1+$AP$32)</f>
         <v>2889471.5064857178</v>
       </c>
       <c r="FN24" s="7">
-        <f t="shared" si="23"/>
+        <f t="shared" si="33"/>
         <v>2918366.221550575</v>
       </c>
       <c r="FO24" s="7">
-        <f t="shared" si="23"/>
+        <f t="shared" si="33"/>
         <v>2947549.8837660807</v>
       </c>
       <c r="FP24" s="7">
-        <f t="shared" si="23"/>
+        <f t="shared" si="33"/>
         <v>2977025.3826037417</v>
       </c>
       <c r="FQ24" s="7">
-        <f t="shared" si="23"/>
+        <f t="shared" si="33"/>
         <v>3006795.6364297792</v>
       </c>
       <c r="FR24" s="7">
-        <f t="shared" si="23"/>
+        <f t="shared" si="33"/>
         <v>3036863.592794077</v>
       </c>
       <c r="FS24" s="7">
-        <f t="shared" si="23"/>
+        <f t="shared" si="33"/>
         <v>3067232.2287220177</v>
       </c>
       <c r="FT24" s="7">
-        <f t="shared" si="23"/>
+        <f t="shared" si="33"/>
         <v>3097904.5510092378</v>
       </c>
       <c r="FU24" s="7">
-        <f t="shared" si="23"/>
+        <f t="shared" si="33"/>
         <v>3128883.5965193301</v>
       </c>
       <c r="FV24" s="7">
-        <f t="shared" si="23"/>
+        <f t="shared" si="33"/>
         <v>3160172.4324845234</v>
       </c>
       <c r="FW24" s="7">
-        <f t="shared" si="23"/>
+        <f t="shared" si="33"/>
         <v>3191774.1568093686</v>
       </c>
       <c r="FX24" s="7">
-        <f t="shared" si="23"/>
+        <f t="shared" si="33"/>
         <v>3223691.8983774623</v>
       </c>
       <c r="FY24" s="7">
-        <f t="shared" si="23"/>
+        <f t="shared" si="33"/>
         <v>3255928.817361237</v>
       </c>
       <c r="FZ24" s="7">
-        <f t="shared" si="23"/>
+        <f t="shared" si="33"/>
         <v>3288488.1055348492</v>
       </c>
       <c r="GA24" s="7">
-        <f t="shared" si="23"/>
+        <f t="shared" si="33"/>
         <v>3321372.9865901978</v>
       </c>
       <c r="GB24" s="7">
-        <f t="shared" si="23"/>
+        <f t="shared" si="33"/>
         <v>3354586.7164560999</v>
       </c>
       <c r="GC24" s="7">
-        <f t="shared" si="23"/>
+        <f t="shared" si="33"/>
         <v>3388132.5836206609</v>
       </c>
       <c r="GD24" s="7">
-        <f t="shared" si="23"/>
+        <f t="shared" si="33"/>
         <v>3422013.9094568677</v>
       </c>
       <c r="GE24" s="7">
-        <f t="shared" si="23"/>
+        <f t="shared" si="33"/>
         <v>3456234.0485514365</v>
       </c>
       <c r="GF24" s="7">
-        <f t="shared" ref="GF24:GW24" si="24">+GE24*(1+$AP$32)</f>
+        <f t="shared" ref="GF24:GW24" si="34">+GE24*(1+$AP$32)</f>
         <v>3490796.3890369511</v>
       </c>
       <c r="GG24" s="7">
-        <f t="shared" si="24"/>
+        <f t="shared" si="34"/>
         <v>3525704.3529273206</v>
       </c>
       <c r="GH24" s="7">
-        <f t="shared" si="24"/>
+        <f t="shared" si="34"/>
         <v>3560961.3964565936</v>
       </c>
       <c r="GI24" s="7">
-        <f t="shared" si="24"/>
+        <f t="shared" si="34"/>
         <v>3596571.0104211597</v>
       </c>
       <c r="GJ24" s="7">
-        <f t="shared" si="24"/>
+        <f t="shared" si="34"/>
         <v>3632536.7205253714</v>
       </c>
       <c r="GK24" s="7">
-        <f t="shared" si="24"/>
+        <f t="shared" si="34"/>
         <v>3668862.0877306252</v>
       </c>
       <c r="GL24" s="7">
-        <f t="shared" si="24"/>
+        <f t="shared" si="34"/>
         <v>3705550.7086079316</v>
       </c>
       <c r="GM24" s="7">
-        <f t="shared" si="24"/>
+        <f t="shared" si="34"/>
         <v>3742606.2156940112</v>
       </c>
       <c r="GN24" s="7">
-        <f t="shared" si="24"/>
+        <f t="shared" si="34"/>
         <v>3780032.2778509515</v>
       </c>
       <c r="GO24" s="7">
-        <f t="shared" si="24"/>
+        <f t="shared" si="34"/>
         <v>3817832.600629461</v>
       </c>
       <c r="GP24" s="7">
-        <f t="shared" si="24"/>
+        <f t="shared" si="34"/>
         <v>3856010.9266357557</v>
       </c>
       <c r="GQ24" s="7">
-        <f t="shared" si="24"/>
+        <f t="shared" si="34"/>
         <v>3894571.0359021132</v>
       </c>
       <c r="GR24" s="7">
-        <f t="shared" si="24"/>
+        <f t="shared" si="34"/>
         <v>3933516.7462611343</v>
       </c>
       <c r="GS24" s="7">
-        <f t="shared" si="24"/>
+        <f t="shared" si="34"/>
         <v>3972851.9137237458</v>
       </c>
       <c r="GT24" s="7">
-        <f t="shared" si="24"/>
+        <f t="shared" si="34"/>
         <v>4012580.4328609835</v>
       </c>
       <c r="GU24" s="7">
-        <f t="shared" si="24"/>
+        <f t="shared" si="34"/>
         <v>4052706.2371895933</v>
       </c>
       <c r="GV24" s="7">
-        <f t="shared" si="24"/>
+        <f t="shared" si="34"/>
         <v>4093233.2995614894</v>
       </c>
       <c r="GW24" s="7">
-        <f t="shared" si="24"/>
+        <f t="shared" si="34"/>
         <v>4134165.6325571043</v>
       </c>
       <c r="GX24" s="7">
-        <f t="shared" ref="GX24:HJ24" si="25">+GW24*(1+$AP$32)</f>
+        <f t="shared" ref="GX24:HJ24" si="35">+GW24*(1+$AP$32)</f>
         <v>4175507.2888826756</v>
       </c>
       <c r="GY24" s="7">
-        <f t="shared" si="25"/>
+        <f t="shared" si="35"/>
         <v>4217262.3617715025</v>
       </c>
       <c r="GZ24" s="7">
-        <f t="shared" si="25"/>
+        <f t="shared" si="35"/>
         <v>4259434.9853892177</v>
       </c>
       <c r="HA24" s="7">
-        <f t="shared" si="25"/>
+        <f t="shared" si="35"/>
         <v>4302029.3352431096</v>
       </c>
       <c r="HB24" s="7">
-        <f t="shared" si="25"/>
+        <f t="shared" si="35"/>
         <v>4345049.6285955403</v>
       </c>
       <c r="HC24" s="7">
-        <f t="shared" si="25"/>
+        <f t="shared" si="35"/>
         <v>4388500.1248814957</v>
       </c>
       <c r="HD24" s="7">
-        <f t="shared" si="25"/>
+        <f t="shared" si="35"/>
         <v>4432385.1261303108</v>
       </c>
       <c r="HE24" s="7">
-        <f t="shared" si="25"/>
+        <f t="shared" si="35"/>
         <v>4476708.9773916136</v>
       </c>
       <c r="HF24" s="7">
-        <f t="shared" si="25"/>
+        <f t="shared" si="35"/>
         <v>4521476.0671655303</v>
       </c>
       <c r="HG24" s="7">
-        <f t="shared" si="25"/>
+        <f t="shared" si="35"/>
         <v>4566690.8278371859</v>
       </c>
       <c r="HH24" s="7">
-        <f t="shared" si="25"/>
+        <f t="shared" si="35"/>
         <v>4612357.7361155581</v>
       </c>
       <c r="HI24" s="7">
-        <f t="shared" si="25"/>
+        <f t="shared" si="35"/>
         <v>4658481.3134767134</v>
       </c>
       <c r="HJ24" s="7">
-        <f t="shared" si="25"/>
+        <f t="shared" si="35"/>
         <v>4705066.1266114805</v>
       </c>
       <c r="HK24" s="7">
-        <f t="shared" ref="HK24:HU24" si="26">+HJ24*(1+$AP$32)</f>
+        <f t="shared" ref="HK24:HU24" si="36">+HJ24*(1+$AP$32)</f>
         <v>4752116.7878775951</v>
       </c>
       <c r="HL24" s="7">
-        <f t="shared" si="26"/>
+        <f t="shared" si="36"/>
         <v>4799637.9557563709</v>
       </c>
       <c r="HM24" s="7">
-        <f t="shared" si="26"/>
+        <f t="shared" si="36"/>
         <v>4847634.3353139348</v>
       </c>
       <c r="HN24" s="7">
-        <f t="shared" si="26"/>
+        <f t="shared" si="36"/>
         <v>4896110.6786670741</v>
       </c>
       <c r="HO24" s="7">
-        <f t="shared" si="26"/>
+        <f t="shared" si="36"/>
         <v>4945071.7854537452</v>
       </c>
       <c r="HP24" s="7">
-        <f t="shared" si="26"/>
+        <f t="shared" si="36"/>
         <v>4994522.5033082822</v>
       </c>
       <c r="HQ24" s="7">
-        <f t="shared" si="26"/>
+        <f t="shared" si="36"/>
         <v>5044467.7283413652</v>
       </c>
       <c r="HR24" s="7">
-        <f t="shared" si="26"/>
+        <f t="shared" si="36"/>
         <v>5094912.4056247789</v>
       </c>
       <c r="HS24" s="7">
-        <f t="shared" si="26"/>
+        <f t="shared" si="36"/>
         <v>5145861.5296810269</v>
       </c>
       <c r="HT24" s="7">
-        <f t="shared" si="26"/>
+        <f t="shared" si="36"/>
         <v>5197320.1449778369</v>
       </c>
       <c r="HU24" s="7">
-        <f t="shared" si="26"/>
+        <f t="shared" si="36"/>
         <v>5249293.3464276157</v>
       </c>
       <c r="HV24" s="7">
-        <f>+HU24*(1+$AP$32)</f>
+        <f t="shared" ref="HV24:IE24" si="37">+HU24*(1+$AP$32)</f>
         <v>5301786.2798918923</v>
       </c>
       <c r="HW24" s="7">
-        <f>+HV24*(1+$AP$32)</f>
+        <f t="shared" si="37"/>
         <v>5354804.1426908113</v>
       </c>
       <c r="HX24" s="7">
-        <f>+HW24*(1+$AP$32)</f>
+        <f t="shared" si="37"/>
         <v>5408352.1841177195</v>
       </c>
       <c r="HY24" s="7">
-        <f>+HX24*(1+$AP$32)</f>
+        <f t="shared" si="37"/>
         <v>5462435.7059588963</v>
       </c>
       <c r="HZ24" s="7">
-        <f>+HY24*(1+$AP$32)</f>
+        <f t="shared" si="37"/>
         <v>5517060.063018485</v>
       </c>
       <c r="IA24" s="7">
-        <f>+HZ24*(1+$AP$32)</f>
+        <f t="shared" si="37"/>
         <v>5572230.6636486696</v>
       </c>
       <c r="IB24" s="7">
-        <f>+IA24*(1+$AP$32)</f>
+        <f t="shared" si="37"/>
         <v>5627952.9702851567</v>
       </c>
       <c r="IC24" s="7">
-        <f>+IB24*(1+$AP$32)</f>
+        <f t="shared" si="37"/>
         <v>5684232.4999880083</v>
       </c>
       <c r="ID24" s="7">
-        <f>+IC24*(1+$AP$32)</f>
+        <f t="shared" si="37"/>
         <v>5741074.8249878883</v>
       </c>
       <c r="IE24" s="7">
-        <f>+ID24*(1+$AP$32)</f>
+        <f t="shared" si="37"/>
         <v>5798485.5732377674</v>
       </c>
     </row>
     <row r="25" spans="2:239" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B25" s="4"/>
       <c r="Y25" s="5">
-        <f t="shared" ref="Y25:AC25" si="27">+Y21/Y20</f>
+        <f t="shared" ref="Y25:AB25" si="38">+Y21/Y20</f>
         <v>-2.098447781339632E-2</v>
       </c>
       <c r="Z25" s="5">
-        <f t="shared" si="27"/>
+        <f t="shared" si="38"/>
         <v>6.1644122012920494E-2</v>
       </c>
       <c r="AA25" s="5">
-        <f t="shared" si="27"/>
+        <f t="shared" si="38"/>
         <v>9.2589629434409793E-2</v>
       </c>
       <c r="AB25" s="5">
-        <f t="shared" si="27"/>
+        <f t="shared" si="38"/>
         <v>8.9302003711742323E-2</v>
       </c>
       <c r="AC25" s="5">
@@ -4613,83 +4601,83 @@
         <v>15</v>
       </c>
       <c r="G28" s="5">
-        <f>+G11/C11-1</f>
+        <f t="shared" ref="G28:K31" si="39">+G11/C11-1</f>
         <v>0.51527005559968231</v>
       </c>
       <c r="H28" s="5">
-        <f>+H11/D11-1</f>
+        <f t="shared" si="39"/>
         <v>0.43450575037042261</v>
       </c>
       <c r="I28" s="5">
-        <f>+I11/E11-1</f>
+        <f t="shared" si="39"/>
         <v>0.40588004940205447</v>
       </c>
       <c r="J28" s="5">
-        <f>+J11/F11-1</f>
+        <f t="shared" si="39"/>
         <v>0.31905845793182408</v>
       </c>
       <c r="K28" s="5">
-        <f>+K11/G11-1</f>
+        <f t="shared" si="39"/>
         <v>0.140101429713402</v>
       </c>
       <c r="Y28" s="5">
-        <f>+Y11/X11-1</f>
+        <f t="shared" ref="Y28:AC30" si="40">+Y11/X11-1</f>
         <v>0.26263202217621662</v>
       </c>
       <c r="Z28" s="5">
-        <f>+Z11/Y11-1</f>
+        <f t="shared" si="40"/>
         <v>0.5775732101295723</v>
       </c>
       <c r="AA28" s="5">
-        <f>+AA11/Z11-1</f>
+        <f t="shared" si="40"/>
         <v>-1.0728063839906987E-2</v>
       </c>
       <c r="AB28" s="5">
-        <f>+AB11/AA11-1</f>
+        <f t="shared" si="40"/>
         <v>9.8752626518038289E-2</v>
       </c>
       <c r="AC28" s="5">
-        <f>+AC11/AB11-1</f>
+        <f t="shared" si="40"/>
         <v>0.40896622976723451</v>
       </c>
       <c r="AD28" s="5">
-        <f t="shared" ref="AD28:AM28" si="28">+AD11/AC11-1</f>
+        <f t="shared" ref="AD28:AM28" si="41">+AD11/AC11-1</f>
         <v>0.19999999999999996</v>
       </c>
       <c r="AE28" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="41"/>
         <v>0.15999999999999992</v>
       </c>
       <c r="AF28" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="41"/>
         <v>0.15999999999999992</v>
       </c>
       <c r="AG28" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="41"/>
         <v>0.15999999999999992</v>
       </c>
       <c r="AH28" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="41"/>
         <v>0.15999999999999992</v>
       </c>
       <c r="AI28" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="41"/>
         <v>0.15999999999999992</v>
       </c>
       <c r="AJ28" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="41"/>
         <v>0.15999999999999992</v>
       </c>
       <c r="AK28" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="41"/>
         <v>0.1599999999999997</v>
       </c>
       <c r="AL28" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="41"/>
         <v>0.15999999999999992</v>
       </c>
       <c r="AM28" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="41"/>
         <v>0.15999999999999992</v>
       </c>
     </row>
@@ -4698,83 +4686,83 @@
         <v>16</v>
       </c>
       <c r="G29" s="5">
-        <f>+G12/C12-1</f>
+        <f t="shared" si="39"/>
         <v>0.55815569972196477</v>
       </c>
       <c r="H29" s="5">
-        <f>+H12/D12-1</f>
+        <f t="shared" si="39"/>
         <v>0.21686768357573616</v>
       </c>
       <c r="I29" s="5">
-        <f>+I12/E12-1</f>
+        <f t="shared" si="39"/>
         <v>1.5833398330863391E-2</v>
       </c>
       <c r="J29" s="5">
-        <f>+J12/F12-1</f>
+        <f t="shared" si="39"/>
         <v>0.23131366923777286</v>
       </c>
       <c r="K29" s="5">
-        <f>+K12/G12-1</f>
+        <f t="shared" si="39"/>
         <v>0</v>
       </c>
       <c r="Y29" s="5">
-        <f>+Y12/X12-1</f>
+        <f t="shared" si="40"/>
         <v>0.61667455061494802</v>
       </c>
       <c r="Z29" s="5">
-        <f>+Z12/Y12-1</f>
+        <f t="shared" si="40"/>
         <v>2.2749550129474994E-2</v>
       </c>
       <c r="AA29" s="5">
-        <f>+AA12/Z12-1</f>
+        <f t="shared" si="40"/>
         <v>7.3625336156090793E-2</v>
       </c>
       <c r="AB29" s="5">
-        <f>+AB12/AA12-1</f>
+        <f t="shared" si="40"/>
         <v>0.5067084138298581</v>
       </c>
       <c r="AC29" s="5">
-        <f>+AC12/AB12-1</f>
+        <f t="shared" si="40"/>
         <v>0.23524574217851901</v>
       </c>
       <c r="AD29" s="5">
-        <f t="shared" ref="AD29:AM29" si="29">+AD12/AC12-1</f>
+        <f t="shared" ref="AD29:AM29" si="42">+AD12/AC12-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AE29" s="5">
-        <f t="shared" si="29"/>
+        <f t="shared" si="42"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AF29" s="5">
-        <f t="shared" si="29"/>
+        <f t="shared" si="42"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AG29" s="5">
-        <f t="shared" si="29"/>
+        <f t="shared" si="42"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AH29" s="5">
-        <f t="shared" si="29"/>
+        <f t="shared" si="42"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AI29" s="5">
-        <f t="shared" si="29"/>
+        <f t="shared" si="42"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AJ29" s="5">
-        <f t="shared" si="29"/>
+        <f t="shared" si="42"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AK29" s="5">
-        <f t="shared" si="29"/>
+        <f t="shared" si="42"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AL29" s="5">
-        <f t="shared" si="29"/>
+        <f t="shared" si="42"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AM29" s="5">
-        <f t="shared" si="29"/>
+        <f t="shared" si="42"/>
         <v>1.0000000000000009E-2</v>
       </c>
     </row>
@@ -4783,83 +4771,83 @@
         <v>17</v>
       </c>
       <c r="G30" s="5">
-        <f>+G13/C13-1</f>
+        <f t="shared" si="39"/>
         <v>-0.18243074619416022</v>
       </c>
       <c r="H30" s="5">
-        <f>+H13/D13-1</f>
+        <f t="shared" si="39"/>
         <v>0.16841497954473938</v>
       </c>
       <c r="I30" s="5">
-        <f>+I13/E13-1</f>
+        <f t="shared" si="39"/>
         <v>0.33548687891301454</v>
       </c>
       <c r="J30" s="5">
-        <f>+J13/F13-1</f>
+        <f t="shared" si="39"/>
         <v>-0.26190637490684909</v>
       </c>
       <c r="K30" s="5">
-        <f>+K13/G13-1</f>
+        <f t="shared" si="39"/>
         <v>0.4652014652014651</v>
       </c>
       <c r="Y30" s="5">
-        <f>+Y13/X13-1</f>
+        <f t="shared" si="40"/>
         <v>-2.1563455177322499E-3</v>
       </c>
       <c r="Z30" s="5">
-        <f>+Z13/Y13-1</f>
+        <f t="shared" si="40"/>
         <v>0.84438663113945833</v>
       </c>
       <c r="AA30" s="5">
-        <f>+AA13/Z13-1</f>
+        <f t="shared" si="40"/>
         <v>-1.7449862926435245E-2</v>
       </c>
       <c r="AB30" s="5">
-        <f>+AB13/AA13-1</f>
+        <f t="shared" si="40"/>
         <v>-3.1698986975397969E-2</v>
       </c>
       <c r="AC30" s="5">
-        <f>+AC13/AB13-1</f>
+        <f t="shared" si="40"/>
         <v>-3.7531236175376903E-2</v>
       </c>
       <c r="AD30" s="5">
-        <f t="shared" ref="AD30:AM30" si="30">+AD13/AC13-1</f>
+        <f t="shared" ref="AD30:AM30" si="43">+AD13/AC13-1</f>
         <v>8.0000000000000071E-2</v>
       </c>
       <c r="AE30" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="43"/>
         <v>8.0000000000000071E-2</v>
       </c>
       <c r="AF30" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="43"/>
         <v>8.0000000000000071E-2</v>
       </c>
       <c r="AG30" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="43"/>
         <v>8.0000000000000071E-2</v>
       </c>
       <c r="AH30" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="43"/>
         <v>8.0000000000000071E-2</v>
       </c>
       <c r="AI30" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="43"/>
         <v>8.0000000000000071E-2</v>
       </c>
       <c r="AJ30" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="43"/>
         <v>8.0000000000000071E-2</v>
       </c>
       <c r="AK30" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="43"/>
         <v>8.0000000000000071E-2</v>
       </c>
       <c r="AL30" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="43"/>
         <v>8.0000000000000071E-2</v>
       </c>
       <c r="AM30" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="43"/>
         <v>8.0000000000000071E-2</v>
       </c>
     </row>
@@ -4868,51 +4856,51 @@
         <v>18</v>
       </c>
       <c r="G31" s="5">
-        <f>+G14/C14-1</f>
+        <f t="shared" si="39"/>
         <v>0.41395254133756398</v>
       </c>
       <c r="H31" s="5">
-        <f>+H14/D14-1</f>
+        <f t="shared" si="39"/>
         <v>0.30325114652862917</v>
       </c>
       <c r="I31" s="5">
-        <f>+I14/E14-1</f>
+        <f t="shared" si="39"/>
         <v>0.22678386123576577</v>
       </c>
       <c r="J31" s="5">
-        <f>+J14/F14-1</f>
+        <f t="shared" si="39"/>
         <v>0.18089160904271817</v>
       </c>
       <c r="K31" s="5">
-        <f>+K14/G14-1</f>
+        <f t="shared" si="39"/>
         <v>0.10986775788412606</v>
       </c>
       <c r="U31" s="5">
-        <f t="shared" ref="T31:AA31" si="31">+U14/T14-1</f>
+        <f t="shared" ref="U31:AA31" si="44">+U14/T14-1</f>
         <v>0.1678550207961973</v>
       </c>
       <c r="V31" s="5">
-        <f t="shared" si="31"/>
+        <f t="shared" si="44"/>
         <v>-0.41185448995166629</v>
       </c>
       <c r="W31" s="5">
-        <f t="shared" si="31"/>
+        <f t="shared" si="44"/>
         <v>-1.557093425605538E-2</v>
       </c>
       <c r="X31" s="5">
-        <f t="shared" si="31"/>
+        <f t="shared" si="44"/>
         <v>8.2258347978910296E-2</v>
       </c>
       <c r="Y31" s="5">
-        <f t="shared" si="31"/>
+        <f t="shared" si="44"/>
         <v>0.33282451425370052</v>
       </c>
       <c r="Z31" s="5">
-        <f t="shared" si="31"/>
+        <f t="shared" si="44"/>
         <v>0.38528010624299425</v>
       </c>
       <c r="AA31" s="5">
-        <f t="shared" si="31"/>
+        <f t="shared" si="44"/>
         <v>1.3905227213259597E-2</v>
       </c>
       <c r="AB31" s="5">
@@ -4924,43 +4912,43 @@
         <v>0.2712890568857973</v>
       </c>
       <c r="AD31" s="5">
-        <f t="shared" ref="AD31:AM31" si="32">+AD14/AC14-1</f>
+        <f t="shared" ref="AD31:AM31" si="45">+AD14/AC14-1</f>
         <v>0.1113356132442096</v>
       </c>
       <c r="AE31" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="45"/>
         <v>9.733482888068079E-2</v>
       </c>
       <c r="AF31" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="45"/>
         <v>0.10175806764136297</v>
       </c>
       <c r="AG31" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="45"/>
         <v>0.10605562530494694</v>
       </c>
       <c r="AH31" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="45"/>
         <v>0.11020043947492009</v>
       </c>
       <c r="AI31" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="45"/>
         <v>0.1141697607006853</v>
       </c>
       <c r="AJ31" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="45"/>
         <v>0.11794548143905659</v>
       </c>
       <c r="AK31" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="45"/>
         <v>0.12151422718535287</v>
       </c>
       <c r="AL31" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="45"/>
         <v>0.12486723415711221</v>
       </c>
       <c r="AM31" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="45"/>
         <v>0.12800005091460065</v>
       </c>
     </row>
@@ -4981,7 +4969,7 @@
         <v>92</v>
       </c>
       <c r="AP33" s="5">
-        <v>7.0000000000000007E-2</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="34" spans="2:42" s="3" customFormat="1" x14ac:dyDescent="0.2">
@@ -4989,35 +4977,35 @@
         <v>30</v>
       </c>
       <c r="C34" s="5">
-        <f>(C11-C15)/C11</f>
+        <f t="shared" ref="C34:J34" si="46">(C11-C15)/C11</f>
         <v>0.60190627482128678</v>
       </c>
       <c r="D34" s="5">
-        <f>(D11-D15)/D11</f>
+        <f t="shared" si="46"/>
         <v>0.59819727651167709</v>
       </c>
       <c r="E34" s="5">
-        <f>(E11-E15)/E11</f>
+        <f t="shared" si="46"/>
         <v>0.63017742567099433</v>
       </c>
       <c r="F34" s="5">
-        <f>(F11-F15)/F11</f>
+        <f t="shared" si="46"/>
         <v>0.61163434147937135</v>
       </c>
       <c r="G34" s="5">
-        <f>(G11-G15)/G11</f>
+        <f t="shared" si="46"/>
         <v>0.59922158592040253</v>
       </c>
       <c r="H34" s="5">
-        <f>(H11-H15)/H11</f>
+        <f t="shared" si="46"/>
         <v>0.60137719028588998</v>
       </c>
       <c r="I34" s="5">
-        <f>(I11-I15)/I11</f>
+        <f t="shared" si="46"/>
         <v>0.63213773006792229</v>
       </c>
       <c r="J34" s="5">
-        <f>(J11-J15)/J11</f>
+        <f t="shared" si="46"/>
         <v>0.61414784351815499</v>
       </c>
       <c r="K34" s="5"/>
@@ -5026,15 +5014,15 @@
       <c r="N34" s="5"/>
       <c r="O34" s="5"/>
       <c r="X34" s="5">
-        <f t="shared" ref="X34:Z34" si="33">(X11-X15)/X11</f>
+        <f t="shared" ref="X34:Z34" si="47">(X11-X15)/X11</f>
         <v>0.66885680199305242</v>
       </c>
       <c r="Y34" s="5">
-        <f t="shared" si="33"/>
+        <f t="shared" si="47"/>
         <v>0.65681036579011365</v>
       </c>
       <c r="Z34" s="5">
-        <f t="shared" si="33"/>
+        <f t="shared" si="47"/>
         <v>0.60815262388359437</v>
       </c>
       <c r="AA34" s="5">
@@ -5054,7 +5042,7 @@
       </c>
       <c r="AP34" s="3">
         <f>NPV(AP33,AD24:IE24)</f>
-        <v>10159735.295051966</v>
+        <v>8498380.3596068583</v>
       </c>
     </row>
     <row r="35" spans="2:42" s="3" customFormat="1" x14ac:dyDescent="0.2">
@@ -5062,35 +5050,35 @@
         <v>32</v>
       </c>
       <c r="C35" s="5">
-        <f>+C17/C14</f>
+        <f t="shared" ref="C35:J35" si="48">+C17/C14</f>
         <v>0.82520721806042197</v>
       </c>
       <c r="D35" s="5">
-        <f>+D17/D14</f>
+        <f t="shared" si="48"/>
         <v>0.82004419621910429</v>
       </c>
       <c r="E35" s="5">
-        <f>+E17/E14</f>
+        <f t="shared" si="48"/>
         <v>0.82609113962326386</v>
       </c>
       <c r="F35" s="5">
-        <f>+F17/F14</f>
+        <f t="shared" si="48"/>
         <v>0.81865526188377546</v>
       </c>
       <c r="G35" s="5">
-        <f>+G17/G14</f>
+        <f t="shared" si="48"/>
         <v>0.81322301156818511</v>
       </c>
       <c r="H35" s="5">
-        <f>+H17/H14</f>
+        <f t="shared" si="48"/>
         <v>0.80808784674436296</v>
       </c>
       <c r="I35" s="5">
-        <f>+I17/I14</f>
+        <f t="shared" si="48"/>
         <v>0.80467528975480773</v>
       </c>
       <c r="J35" s="5">
-        <f>+J17/J14</f>
+        <f t="shared" si="48"/>
         <v>0.79768087298416768</v>
       </c>
       <c r="K35" s="5"/>
@@ -5099,15 +5087,15 @@
       <c r="N35" s="5"/>
       <c r="O35" s="5"/>
       <c r="X35" s="5">
-        <f t="shared" ref="X35:Z35" si="34">+X17/X14</f>
+        <f t="shared" ref="X35:Z35" si="49">+X17/X14</f>
         <v>0.82382410016157714</v>
       </c>
       <c r="Y35" s="5">
-        <f t="shared" si="34"/>
+        <f t="shared" si="49"/>
         <v>0.83505226862907544</v>
       </c>
       <c r="Z35" s="5">
-        <f t="shared" si="34"/>
+        <f t="shared" si="49"/>
         <v>0.79409533568018853</v>
       </c>
       <c r="AA35" s="5">
@@ -5135,35 +5123,35 @@
         <v>33</v>
       </c>
       <c r="C36" s="5">
-        <f>+C20/C14</f>
+        <f t="shared" ref="C36:J36" si="50">+C20/C14</f>
         <v>0.28914660942895198</v>
       </c>
       <c r="D36" s="5">
-        <f>+D20/D14</f>
+        <f t="shared" si="50"/>
         <v>0.32868667605079538</v>
       </c>
       <c r="E36" s="5">
-        <f>+E20/E14</f>
+        <f t="shared" si="50"/>
         <v>0.3645103873880684</v>
       </c>
       <c r="F36" s="5">
-        <f>+F20/F14</f>
+        <f t="shared" si="50"/>
         <v>0.3736204392248389</v>
       </c>
       <c r="G36" s="5">
-        <f>+G20/G14</f>
+        <f t="shared" si="50"/>
         <v>0.38914822637162194</v>
       </c>
       <c r="H36" s="5">
-        <f>+H20/H14</f>
+        <f t="shared" si="50"/>
         <v>0.4310634171268633</v>
       </c>
       <c r="I36" s="5">
-        <f>+I20/I14</f>
+        <f t="shared" si="50"/>
         <v>0.3640015012912225</v>
       </c>
       <c r="J36" s="5">
-        <f>+J20/J14</f>
+        <f t="shared" si="50"/>
         <v>0.38133659931456443</v>
       </c>
       <c r="K36" s="5"/>
@@ -5172,15 +5160,15 @@
       <c r="N36" s="5"/>
       <c r="O36" s="5"/>
       <c r="X36" s="5">
-        <f t="shared" ref="X36:Z36" si="35">+X20/X14</f>
+        <f t="shared" ref="X36:Z36" si="51">+X20/X14</f>
         <v>-9.4802737879685933E-2</v>
       </c>
       <c r="Y36" s="5">
-        <f t="shared" si="35"/>
+        <f t="shared" si="51"/>
         <v>0.14442711633120522</v>
       </c>
       <c r="Z36" s="5">
-        <f t="shared" si="35"/>
+        <f t="shared" si="51"/>
         <v>0.21034184782967197</v>
       </c>
       <c r="AA36" s="5">
@@ -5200,7 +5188,7 @@
       </c>
       <c r="AP36" s="3">
         <f>+AP34/AP35</f>
-        <v>92.605371388678932</v>
+        <v>77.462221854041189</v>
       </c>
     </row>
     <row r="37" spans="2:42" x14ac:dyDescent="0.2">
@@ -5238,12 +5226,12 @@
       <c r="M38" s="3"/>
       <c r="N38" s="3"/>
       <c r="O38" s="3"/>
-      <c r="AO38" s="17" t="s">
+      <c r="AO38" s="16" t="s">
         <v>104</v>
       </c>
-      <c r="AP38" s="18">
+      <c r="AP38" s="17">
         <f>+AP36/AP37-1</f>
-        <v>-0.13452923935814087</v>
+        <v>-0.27605400136410108</v>
       </c>
     </row>
     <row r="39" spans="2:42" s="3" customFormat="1" x14ac:dyDescent="0.2">
@@ -5813,19 +5801,19 @@
         <v>1120692</v>
       </c>
       <c r="G68" s="3">
-        <f t="shared" ref="G68:J68" si="36">+G65</f>
+        <f t="shared" ref="G68:J68" si="52">+G65</f>
         <v>1159837</v>
       </c>
       <c r="H68" s="3">
-        <f t="shared" si="36"/>
+        <f t="shared" si="52"/>
         <v>1227980</v>
       </c>
       <c r="I68" s="3">
-        <f t="shared" si="36"/>
+        <f t="shared" si="52"/>
         <v>1288498</v>
       </c>
       <c r="J68" s="3">
-        <f t="shared" si="36"/>
+        <f t="shared" si="52"/>
         <v>1364425</v>
       </c>
       <c r="K68" s="3"/>
@@ -5936,31 +5924,31 @@
         <v>81</v>
       </c>
       <c r="C74" s="7">
-        <f>+SUM(C72:C73)</f>
+        <f t="shared" ref="C74:I74" si="53">+SUM(C72:C73)</f>
         <v>36111</v>
       </c>
       <c r="D74" s="7">
-        <f>+SUM(D72:D73)</f>
+        <f t="shared" si="53"/>
         <v>59092</v>
       </c>
       <c r="E74" s="7">
-        <f>+SUM(E72:E73)</f>
+        <f t="shared" si="53"/>
         <v>52204</v>
       </c>
       <c r="F74" s="7">
-        <f>+SUM(F72:F73)</f>
+        <f t="shared" si="53"/>
         <v>52495</v>
       </c>
       <c r="G74" s="7">
-        <f>+SUM(G72:G73)</f>
+        <f t="shared" si="53"/>
         <v>69542</v>
       </c>
       <c r="H74" s="7">
-        <f>+SUM(H72:H73)</f>
+        <f t="shared" si="53"/>
         <v>87852</v>
       </c>
       <c r="I74" s="7">
-        <f>+SUM(I72:I73)</f>
+        <f t="shared" si="53"/>
         <v>82483</v>
       </c>
     </row>
